--- a/semantic model development/foundational_semantic_model_generator/src/foundational_semantic_model_generator/input/SMS + Multicase/tactic-classification-overview.xlsx
+++ b/semantic model development/foundational_semantic_model_generator/src/foundational_semantic_model_generator/input/SMS + Multicase/tactic-classification-overview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phili\Dropbox\01_Dev\02_QualiTact\Repository\QualiTact\semantic model development\foundational_semantic_model_generator\src\foundational_semantic_model_generator\input\SMS + Multicase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C50D3E-4B18-4239-91B4-A4849225DC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D340D063-549E-4D7C-A263-29C8854590F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1692" yWindow="456" windowWidth="16416" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tactics classification overview" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="245">
   <si>
     <t>Category</t>
   </si>
@@ -772,9 +772,6 @@
   </si>
   <si>
     <t>Recovery</t>
-  </si>
-  <si>
-    <t>Training</t>
   </si>
 </sst>
 </file>
@@ -1123,6 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E22A452A-88F0-4E03-ABFB-CF6870FEE69A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1153,7 +1151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>173</v>
       </c>
@@ -1170,7 +1168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>173</v>
       </c>
@@ -1187,7 +1185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>173</v>
       </c>
@@ -1204,7 +1202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>173</v>
       </c>
@@ -1221,7 +1219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>173</v>
       </c>
@@ -1238,7 +1236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>173</v>
       </c>
@@ -1255,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>173</v>
       </c>
@@ -1272,7 +1270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>173</v>
       </c>
@@ -1289,7 +1287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>173</v>
       </c>
@@ -1306,7 +1304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>173</v>
       </c>
@@ -1323,7 +1321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>173</v>
       </c>
@@ -1340,7 +1338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>173</v>
       </c>
@@ -1357,7 +1355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>173</v>
       </c>
@@ -1374,7 +1372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>173</v>
       </c>
@@ -1391,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>173</v>
       </c>
@@ -1408,7 +1406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>173</v>
       </c>
@@ -1425,7 +1423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>173</v>
       </c>
@@ -1442,7 +1440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>173</v>
       </c>
@@ -1459,7 +1457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>173</v>
       </c>
@@ -1476,7 +1474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>173</v>
       </c>
@@ -1493,7 +1491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>173</v>
       </c>
@@ -1510,7 +1508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>173</v>
       </c>
@@ -1527,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>173</v>
       </c>
@@ -1544,7 +1542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>173</v>
       </c>
@@ -1561,7 +1559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>173</v>
       </c>
@@ -1578,7 +1576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>173</v>
       </c>
@@ -1595,7 +1593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>173</v>
       </c>
@@ -1612,7 +1610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>173</v>
       </c>
@@ -1629,7 +1627,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>173</v>
       </c>
@@ -1646,7 +1644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>173</v>
       </c>
@@ -1663,7 +1661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>173</v>
       </c>
@@ -1680,7 +1678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>173</v>
       </c>
@@ -1697,7 +1695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>173</v>
       </c>
@@ -1714,7 +1712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>173</v>
       </c>
@@ -1731,7 +1729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>173</v>
       </c>
@@ -1748,7 +1746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>173</v>
       </c>
@@ -1765,7 +1763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>173</v>
       </c>
@@ -1782,7 +1780,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>173</v>
       </c>
@@ -1799,7 +1797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>173</v>
       </c>
@@ -1816,7 +1814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>173</v>
       </c>
@@ -1833,7 +1831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>173</v>
       </c>
@@ -1850,7 +1848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>173</v>
       </c>
@@ -1867,7 +1865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>173</v>
       </c>
@@ -1884,7 +1882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>173</v>
       </c>
@@ -1901,7 +1899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>173</v>
       </c>
@@ -1918,7 +1916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>173</v>
       </c>
@@ -1935,7 +1933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>173</v>
       </c>
@@ -1952,7 +1950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>173</v>
       </c>
@@ -1969,7 +1967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>173</v>
       </c>
@@ -1986,7 +1984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>173</v>
       </c>
@@ -2003,7 +2001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>173</v>
       </c>
@@ -2020,7 +2018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>173</v>
       </c>
@@ -2037,7 +2035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>173</v>
       </c>
@@ -2054,7 +2052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>173</v>
       </c>
@@ -2071,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>173</v>
       </c>
@@ -2088,7 +2086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>173</v>
       </c>
@@ -2105,7 +2103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>173</v>
       </c>
@@ -2122,7 +2120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>173</v>
       </c>
@@ -2139,7 +2137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>173</v>
       </c>
@@ -2156,7 +2154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>173</v>
       </c>
@@ -2173,7 +2171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>173</v>
       </c>
@@ -2190,7 +2188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>173</v>
       </c>
@@ -2207,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>173</v>
       </c>
@@ -2224,7 +2222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>173</v>
       </c>
@@ -2241,7 +2239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>173</v>
       </c>
@@ -2258,7 +2256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>173</v>
       </c>
@@ -2275,7 +2273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>173</v>
       </c>
@@ -2292,7 +2290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>173</v>
       </c>
@@ -2309,7 +2307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>173</v>
       </c>
@@ -2326,7 +2324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>173</v>
       </c>
@@ -2343,7 +2341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>173</v>
       </c>
@@ -2360,7 +2358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>173</v>
       </c>
@@ -2377,7 +2375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>173</v>
       </c>
@@ -2394,7 +2392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>173</v>
       </c>
@@ -2411,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>173</v>
       </c>
@@ -2425,7 +2423,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>173</v>
       </c>
@@ -2442,7 +2440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>173</v>
       </c>
@@ -2459,7 +2457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>173</v>
       </c>
@@ -2476,7 +2474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>173</v>
       </c>
@@ -2493,7 +2491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>173</v>
       </c>
@@ -2510,7 +2508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>173</v>
       </c>
@@ -2527,7 +2525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>173</v>
       </c>
@@ -2544,7 +2542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>173</v>
       </c>
@@ -2561,7 +2559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>173</v>
       </c>
@@ -2578,7 +2576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>173</v>
       </c>
@@ -2595,7 +2593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>173</v>
       </c>
@@ -2612,7 +2610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>173</v>
       </c>
@@ -2629,7 +2627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>173</v>
       </c>
@@ -2646,7 +2644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>173</v>
       </c>
@@ -2663,7 +2661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>173</v>
       </c>
@@ -2680,7 +2678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>173</v>
       </c>
@@ -2697,7 +2695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>173</v>
       </c>
@@ -2714,7 +2712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>173</v>
       </c>
@@ -2731,7 +2729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>173</v>
       </c>
@@ -2748,7 +2746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>173</v>
       </c>
@@ -2765,7 +2763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>173</v>
       </c>
@@ -2782,7 +2780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>173</v>
       </c>
@@ -2799,7 +2797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>173</v>
       </c>
@@ -2816,7 +2814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>173</v>
       </c>
@@ -2833,7 +2831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>173</v>
       </c>
@@ -2850,7 +2848,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>173</v>
       </c>
@@ -2867,7 +2865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>173</v>
       </c>
@@ -2884,7 +2882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>173</v>
       </c>
@@ -2901,7 +2899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>173</v>
       </c>
@@ -2918,7 +2916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>173</v>
       </c>
@@ -2935,7 +2933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>173</v>
       </c>
@@ -2952,7 +2950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>173</v>
       </c>
@@ -2969,7 +2967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>173</v>
       </c>
@@ -2986,7 +2984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>173</v>
       </c>
@@ -3003,7 +3001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>173</v>
       </c>
@@ -3020,7 +3018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>173</v>
       </c>
@@ -3037,7 +3035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>173</v>
       </c>
@@ -3054,7 +3052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>173</v>
       </c>
@@ -3071,7 +3069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>173</v>
       </c>
@@ -3088,7 +3086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>173</v>
       </c>
@@ -3105,7 +3103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>173</v>
       </c>
@@ -3122,7 +3120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>173</v>
       </c>
@@ -3139,7 +3137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>173</v>
       </c>
@@ -3156,7 +3154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>173</v>
       </c>
@@ -3173,7 +3171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>173</v>
       </c>
@@ -3190,7 +3188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>173</v>
       </c>
@@ -3207,7 +3205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>173</v>
       </c>
@@ -3224,7 +3222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>173</v>
       </c>
@@ -3241,7 +3239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>173</v>
       </c>
@@ -3258,7 +3256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>173</v>
       </c>
@@ -3275,7 +3273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>173</v>
       </c>
@@ -3289,7 +3287,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>173</v>
       </c>
@@ -3306,7 +3304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>173</v>
       </c>
@@ -3697,7 +3695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>237</v>
       </c>
@@ -3711,7 +3709,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>237</v>
       </c>
@@ -3725,7 +3723,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>237</v>
       </c>
@@ -3739,7 +3737,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>237</v>
       </c>
@@ -3753,7 +3751,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>237</v>
       </c>
@@ -3767,7 +3765,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>237</v>
       </c>
@@ -3781,7 +3779,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>237</v>
       </c>
@@ -3795,7 +3793,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>237</v>
       </c>
@@ -3809,7 +3807,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>237</v>
       </c>
@@ -3823,7 +3821,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>237</v>
       </c>
@@ -3837,7 +3835,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>237</v>
       </c>
@@ -3851,7 +3849,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>237</v>
       </c>
@@ -3865,7 +3863,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>237</v>
       </c>
@@ -3879,7 +3877,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>237</v>
       </c>
@@ -3893,7 +3891,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>237</v>
       </c>
@@ -3907,7 +3905,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>237</v>
       </c>
@@ -3921,7 +3919,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>237</v>
       </c>
@@ -3935,7 +3933,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>237</v>
       </c>
@@ -3949,7 +3947,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>237</v>
       </c>
@@ -3963,7 +3961,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>237</v>
       </c>
@@ -3977,7 +3975,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>237</v>
       </c>
@@ -3991,7 +3989,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>237</v>
       </c>
@@ -4005,7 +4003,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>237</v>
       </c>
@@ -4019,7 +4017,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>237</v>
       </c>
@@ -4033,7 +4031,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>237</v>
       </c>
@@ -4047,7 +4045,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>237</v>
       </c>
@@ -4061,7 +4059,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>237</v>
       </c>
@@ -4075,7 +4073,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>237</v>
       </c>
@@ -4089,7 +4087,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>237</v>
       </c>
@@ -4103,7 +4101,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
         <v>237</v>
       </c>
@@ -4117,7 +4115,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>237</v>
       </c>
@@ -4131,7 +4129,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>237</v>
       </c>
@@ -4145,7 +4143,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
         <v>237</v>
       </c>
@@ -4159,7 +4157,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>237</v>
       </c>
@@ -4173,7 +4171,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
         <v>237</v>
       </c>
@@ -4187,7 +4185,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>237</v>
       </c>
@@ -4201,7 +4199,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
         <v>237</v>
       </c>
@@ -4215,7 +4213,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
         <v>237</v>
       </c>
@@ -4229,7 +4227,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
         <v>237</v>
       </c>
@@ -4243,7 +4241,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
         <v>237</v>
       </c>
@@ -4257,7 +4255,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>237</v>
       </c>
@@ -4271,7 +4269,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>237</v>
       </c>
@@ -4285,7 +4283,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>237</v>
       </c>
@@ -4299,7 +4297,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>237</v>
       </c>
@@ -4313,7 +4311,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
         <v>237</v>
       </c>
@@ -4327,7 +4325,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
         <v>237</v>
       </c>
@@ -4341,7 +4339,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
         <v>237</v>
       </c>
@@ -4355,7 +4353,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>237</v>
       </c>
@@ -4369,7 +4367,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>237</v>
       </c>
@@ -4383,7 +4381,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
         <v>237</v>
       </c>
@@ -4397,7 +4395,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>237</v>
       </c>
@@ -4411,7 +4409,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>237</v>
       </c>
@@ -4425,7 +4423,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>237</v>
       </c>
@@ -4439,7 +4437,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>237</v>
       </c>
@@ -4472,7 +4470,7 @@
         <v>237</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>245</v>
+        <v>147</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>233</v>
@@ -4481,7 +4479,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>237</v>
       </c>
@@ -4495,7 +4493,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>237</v>
       </c>
@@ -4509,7 +4507,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>237</v>
       </c>
@@ -4524,7 +4522,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U210" xr:uid="{E22A452A-88F0-4E03-ABFB-CF6870FEE69A}"/>
+  <autoFilter ref="A1:U210" xr:uid="{E22A452A-88F0-4E03-ABFB-CF6870FEE69A}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Traning"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/semantic model development/foundational_semantic_model_generator/src/foundational_semantic_model_generator/input/SMS + Multicase/tactic-classification-overview.xlsx
+++ b/semantic model development/foundational_semantic_model_generator/src/foundational_semantic_model_generator/input/SMS + Multicase/tactic-classification-overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phili\Dropbox\01_Dev\02_QualiTact\Repository\QualiTact\semantic model development\foundational_semantic_model_generator\src\foundational_semantic_model_generator\input\SMS + Multicase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D340D063-549E-4D7C-A263-29C8854590F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A99A9C-6707-47C8-B058-E09AC522AE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,9 +138,6 @@
     <t>ADMM-based compression</t>
   </si>
   <si>
-    <t>Tenary weights</t>
-  </si>
-  <si>
     <t>Parameter amount reduction</t>
   </si>
   <si>
@@ -297,9 +294,6 @@
     <t>Learning Approach</t>
   </si>
   <si>
-    <t>Destillation learning</t>
-  </si>
-  <si>
     <t>Transfer learning</t>
   </si>
   <si>
@@ -772,6 +766,12 @@
   </si>
   <si>
     <t>Recovery</t>
+  </si>
+  <si>
+    <t>Ternary weights</t>
+  </si>
+  <si>
+    <t>Distillation learning</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1120,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E22A452A-88F0-4E03-ABFB-CF6870FEE69A}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1136,24 +1135,24 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1162,15 +1161,15 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E2" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -1179,15 +1178,15 @@
         <v>4</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E3" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -1196,15 +1195,15 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E4" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>6</v>
@@ -1213,15 +1212,15 @@
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E5" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>6</v>
@@ -1230,15 +1229,15 @@
         <v>10</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>6</v>
@@ -1247,15 +1246,15 @@
         <v>11</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>6</v>
@@ -1264,15 +1263,15 @@
         <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E8" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>6</v>
@@ -1281,15 +1280,15 @@
         <v>12</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E9" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>6</v>
@@ -1298,15 +1297,15 @@
         <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E10" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>13</v>
@@ -1315,15 +1314,15 @@
         <v>15</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>13</v>
@@ -1332,15 +1331,15 @@
         <v>14</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>13</v>
@@ -1349,15 +1348,15 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E13" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>17</v>
@@ -1366,15 +1365,15 @@
         <v>19</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E14" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>17</v>
@@ -1383,32 +1382,32 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E15" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E16" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>20</v>
@@ -1417,32 +1416,32 @@
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E17" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>20</v>
@@ -1451,49 +1450,49 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E19" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E20" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E21" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>20</v>
@@ -1502,32 +1501,32 @@
         <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E22" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E23" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>20</v>
@@ -1536,49 +1535,49 @@
         <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E24" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>20</v>
@@ -1587,15 +1586,15 @@
         <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E27" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>20</v>
@@ -1604,15 +1603,15 @@
         <v>22</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E28" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>20</v>
@@ -1621,15 +1620,15 @@
         <v>21</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E29" s="4">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>20</v>
@@ -1638,15 +1637,15 @@
         <v>25</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E30" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>20</v>
@@ -1655,15 +1654,15 @@
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E31" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>20</v>
@@ -1672,32 +1671,32 @@
         <v>23</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E32" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>243</v>
       </c>
       <c r="D33" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E33" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>20</v>
@@ -1706,15 +1705,15 @@
         <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E34" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>20</v>
@@ -1723,1599 +1722,1599 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E35" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E37" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E38" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="D40" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E40" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E41" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E42" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B43" s="4" t="s">
+      <c r="C43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" t="s">
         <v>49</v>
       </c>
-      <c r="C43" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E43" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" t="s">
-        <v>50</v>
-      </c>
       <c r="D44" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E44" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E45" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E46" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E47" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D48" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E48" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E49" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E50" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E51" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E52" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E53" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E54" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D55" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E55" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E56" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E57" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" t="s">
         <v>66</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E58" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" t="s">
-        <v>63</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E59" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" t="s">
-        <v>67</v>
-      </c>
       <c r="D60" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E60" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E61" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E62" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C63" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C63" t="s">
-        <v>64</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E63" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="D64" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E64" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E65" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D66" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E66" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E67" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E68" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E69" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E70" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E71" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" t="s">
         <v>74</v>
       </c>
-      <c r="C72" t="s">
-        <v>75</v>
-      </c>
       <c r="D72" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E72" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" t="s">
+        <v>175</v>
+      </c>
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" t="s">
         <v>83</v>
       </c>
-      <c r="D73" t="s">
-        <v>177</v>
-      </c>
-      <c r="E73" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
+        <v>175</v>
+      </c>
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" t="s">
+        <v>115</v>
+      </c>
+      <c r="D76" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D74" t="s">
-        <v>177</v>
-      </c>
-      <c r="E74" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E75" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B76" t="s">
-        <v>174</v>
-      </c>
-      <c r="C76" t="s">
-        <v>117</v>
-      </c>
-      <c r="D76" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="C77" t="s">
-        <v>86</v>
+        <v>244</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E77" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E78" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E79" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E80" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C81" t="s">
         <v>85</v>
       </c>
-      <c r="C81" t="s">
-        <v>87</v>
-      </c>
       <c r="D81" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E81" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" t="s">
         <v>91</v>
       </c>
-      <c r="C82" t="s">
-        <v>93</v>
-      </c>
       <c r="D82" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E82" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C83" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E83" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C84" t="s">
+        <v>92</v>
+      </c>
+      <c r="D84" t="s">
+        <v>175</v>
+      </c>
+      <c r="E84" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" t="s">
+        <v>95</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" t="s">
         <v>94</v>
       </c>
-      <c r="D84" t="s">
-        <v>177</v>
-      </c>
-      <c r="E84" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="D87" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C88" t="s">
         <v>97</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E85" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="D88" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E88" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C89" t="s">
+        <v>99</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C90" t="s">
+        <v>96</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E90" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E86" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C87" t="s">
-        <v>96</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E87" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C88" t="s">
-        <v>99</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E88" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="C91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C92" t="s">
         <v>101</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E89" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C90" t="s">
-        <v>98</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E90" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C91" t="s">
-        <v>104</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E91" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="D92" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E92" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E92" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B93" s="4" t="s">
+      <c r="C93" t="s">
+        <v>109</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E93" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94" t="s">
         <v>105</v>
       </c>
-      <c r="C93" t="s">
-        <v>111</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E93" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C94" t="s">
-        <v>107</v>
-      </c>
       <c r="D94" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E94" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E95" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C96" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E96" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E97" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E98" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E99" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E100" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C101" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E101" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E102" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C103" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E103" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C104" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E104" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C105" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E105" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B106" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C106" t="s">
+        <v>120</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C107" t="s">
         <v>114</v>
       </c>
-      <c r="C106" t="s">
-        <v>122</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E106" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C107" t="s">
-        <v>116</v>
-      </c>
       <c r="D107" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E107" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B108" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C108" t="s">
+        <v>125</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C109" t="s">
+        <v>124</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E109" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110" t="s">
         <v>123</v>
       </c>
-      <c r="C108" t="s">
-        <v>127</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E108" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C109" t="s">
-        <v>126</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E109" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C110" t="s">
-        <v>125</v>
-      </c>
       <c r="D110" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E110" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C111" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E111" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B112" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C112" t="s">
+        <v>132</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E112" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C113" t="s">
+        <v>131</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E113" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C114" t="s">
         <v>128</v>
       </c>
-      <c r="C112" t="s">
-        <v>134</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E112" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C113" t="s">
-        <v>133</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E113" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C114" t="s">
-        <v>130</v>
-      </c>
       <c r="D114" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E114" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C115" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E115" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C116" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E116" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C117" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E117" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C118" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E118" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C119" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D119" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E119" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C120" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E120" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C121" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E121" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C122" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E122" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E123" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C124" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E124" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C125" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E125" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B126" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C126" t="s">
+        <v>142</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B127" t="s">
+        <v>135</v>
+      </c>
+      <c r="C127" t="s">
+        <v>60</v>
+      </c>
+      <c r="D127" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C126" t="s">
-        <v>144</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E126" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B127" t="s">
-        <v>137</v>
-      </c>
-      <c r="C127" t="s">
-        <v>61</v>
-      </c>
-      <c r="D127" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="D128" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E128" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C129" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E129" s="4">
         <v>5</v>
@@ -3323,16 +3322,16 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C130" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E130" s="4">
         <v>1</v>
@@ -3340,16 +3339,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C131" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E131" s="4">
         <v>28</v>
@@ -3357,16 +3356,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C132" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E132" s="4">
         <v>1</v>
@@ -3374,16 +3373,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C133" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E133" s="4">
         <v>4</v>
@@ -3391,16 +3390,16 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C134" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E134" s="4">
         <v>9</v>
@@ -3408,16 +3407,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D135" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E135" s="4">
         <v>1</v>
@@ -3425,16 +3424,16 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C136" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E136" s="4">
         <v>2</v>
@@ -3442,16 +3441,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C137" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D137" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E137" s="4">
         <v>2</v>
@@ -3459,16 +3458,16 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C138" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E138" s="4">
         <v>2</v>
@@ -3476,16 +3475,16 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E139" s="4">
         <v>1</v>
@@ -3493,16 +3492,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E140" s="4">
         <v>3</v>
@@ -3510,16 +3509,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E141" s="4">
         <v>8</v>
@@ -3527,16 +3526,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C142" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D142" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E142" s="4">
         <v>3</v>
@@ -3544,16 +3543,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C143" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D143" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E143" s="4">
         <v>1</v>
@@ -3561,16 +3560,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C144" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E144" s="4">
         <v>1</v>
@@ -3578,16 +3577,16 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D145" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E145" s="4">
         <v>1</v>
@@ -3595,16 +3594,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C146" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E146" s="4">
         <v>5</v>
@@ -3612,16 +3611,16 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B147" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C147" t="s">
         <v>147</v>
       </c>
-      <c r="C147" t="s">
-        <v>149</v>
-      </c>
       <c r="D147" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E147" s="4">
         <v>11</v>
@@ -3629,16 +3628,16 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D148" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E148" s="4">
         <v>2</v>
@@ -3646,16 +3645,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D149" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E149" s="4">
         <v>1</v>
@@ -3663,16 +3662,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C150" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D150" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E150" s="4">
         <v>2</v>
@@ -3680,855 +3679,849 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C151" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D151" t="s">
+        <v>175</v>
+      </c>
+      <c r="E151" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C153" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E151" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B152" s="4" t="s">
+      <c r="D153" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B154" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C154" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D152" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C153" s="4" t="s">
+      <c r="D154" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D153" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="D155" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C156" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D156" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="4" t="s">
+      <c r="D158" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B190" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B157" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D158" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D159" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D160" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D161" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D165" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D167" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D169" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D172" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D173" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D174" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D176" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D177" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="D178" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D180" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D181" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="D182" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D183" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D184" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D185" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D186" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="D187" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C188" s="4" t="s">
+      <c r="C190" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D188" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D189" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B190" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>216</v>
-      </c>
       <c r="D190" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C191" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C193" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D191" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C192" s="4" t="s">
+      <c r="D193" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C194" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D192" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C193" s="4" t="s">
+      <c r="D194" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C195" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D193" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C194" s="4" t="s">
+      <c r="D195" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C196" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="D194" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C195" s="4" t="s">
+      <c r="D196" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C197" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D195" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C196" s="4" t="s">
+      <c r="D197" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C198" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D196" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C197" s="4" t="s">
+      <c r="D198" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C199" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="D197" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C198" s="4" t="s">
+      <c r="D199" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C200" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D198" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C199" s="4" t="s">
+      <c r="D200" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C201" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D199" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C200" s="4" t="s">
+      <c r="D201" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D200" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B201" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C201" s="4" t="s">
+      <c r="D202" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C203" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D201" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C202" s="4" t="s">
+      <c r="D203" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A204" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C204" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D202" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C203" s="4" t="s">
+      <c r="D204" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C205" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D203" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D204" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B205" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="D205" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C207" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C209" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="D207" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B208" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C208" s="4" t="s">
+      <c r="D209" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D208" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B209" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D209" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B210" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>236</v>
-      </c>
       <c r="D210" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U210" xr:uid="{E22A452A-88F0-4E03-ABFB-CF6870FEE69A}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Traning"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U210" xr:uid="{E22A452A-88F0-4E03-ABFB-CF6870FEE69A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
